--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\wnba\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795ED4F0-E0E0-4503-8422-AB0DB130041D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3BE862-7B53-4987-916E-EAAE27925868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -16396,8 +16396,17 @@
       <c r="G496" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H496">
+        <v>88</v>
+      </c>
+      <c r="I496">
+        <v>94</v>
+      </c>
+      <c r="J496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="497" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>46246</v>
       </c>
@@ -16419,8 +16428,17 @@
       <c r="G497" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H497">
+        <v>94</v>
+      </c>
+      <c r="I497">
+        <v>88</v>
+      </c>
+      <c r="J497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="498" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>46246</v>
       </c>
@@ -16442,8 +16460,17 @@
       <c r="G498" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H498">
+        <v>71</v>
+      </c>
+      <c r="I498">
+        <v>91</v>
+      </c>
+      <c r="J498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>46246</v>
       </c>
@@ -16465,8 +16492,17 @@
       <c r="G499" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H499">
+        <v>91</v>
+      </c>
+      <c r="I499">
+        <v>71</v>
+      </c>
+      <c r="J499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>46246</v>
       </c>
@@ -16488,8 +16524,17 @@
       <c r="G500" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H500">
+        <v>85</v>
+      </c>
+      <c r="I500">
+        <v>81</v>
+      </c>
+      <c r="J500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>46246</v>
       </c>
@@ -16511,8 +16556,17 @@
       <c r="G501" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H501">
+        <v>81</v>
+      </c>
+      <c r="I501">
+        <v>85</v>
+      </c>
+      <c r="J501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>46247</v>
       </c>
@@ -16535,7 +16589,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>46247</v>
       </c>
@@ -16558,7 +16612,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>46247</v>
       </c>
@@ -16581,7 +16635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>46247</v>
       </c>
@@ -16604,7 +16658,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>46247</v>
       </c>
@@ -16627,7 +16681,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>46247</v>
       </c>
@@ -16650,7 +16704,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>46248</v>
       </c>
@@ -16673,7 +16727,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>46248</v>
       </c>
@@ -16696,7 +16750,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>46248</v>
       </c>
@@ -16719,7 +16773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>46248</v>
       </c>
@@ -16742,7 +16796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>46249</v>
       </c>

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3BE862-7B53-4987-916E-EAAE27925868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965A25A3-FB99-4083-9435-3BC0AB26DB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -16588,6 +16588,15 @@
       <c r="G502" t="s">
         <v>24</v>
       </c>
+      <c r="H502">
+        <v>104</v>
+      </c>
+      <c r="I502">
+        <v>69</v>
+      </c>
+      <c r="J502">
+        <v>0</v>
+      </c>
     </row>
     <row r="503" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
@@ -16611,6 +16620,15 @@
       <c r="G503" t="s">
         <v>25</v>
       </c>
+      <c r="H503">
+        <v>69</v>
+      </c>
+      <c r="I503">
+        <v>104</v>
+      </c>
+      <c r="J503">
+        <v>0</v>
+      </c>
     </row>
     <row r="504" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
@@ -16634,6 +16652,15 @@
       <c r="G504" t="s">
         <v>24</v>
       </c>
+      <c r="H504">
+        <v>76</v>
+      </c>
+      <c r="I504">
+        <v>83</v>
+      </c>
+      <c r="J504">
+        <v>0</v>
+      </c>
     </row>
     <row r="505" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
@@ -16657,6 +16684,15 @@
       <c r="G505" t="s">
         <v>25</v>
       </c>
+      <c r="H505">
+        <v>83</v>
+      </c>
+      <c r="I505">
+        <v>76</v>
+      </c>
+      <c r="J505">
+        <v>0</v>
+      </c>
     </row>
     <row r="506" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
@@ -16680,6 +16716,15 @@
       <c r="G506" t="s">
         <v>24</v>
       </c>
+      <c r="H506">
+        <v>81</v>
+      </c>
+      <c r="I506">
+        <v>85</v>
+      </c>
+      <c r="J506">
+        <v>0</v>
+      </c>
     </row>
     <row r="507" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
@@ -16702,6 +16747,15 @@
       </c>
       <c r="G507" t="s">
         <v>25</v>
+      </c>
+      <c r="H507">
+        <v>85</v>
+      </c>
+      <c r="I507">
+        <v>81</v>
+      </c>
+      <c r="J507">
+        <v>0</v>
       </c>
     </row>
     <row r="508" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965A25A3-FB99-4083-9435-3BC0AB26DB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F851A15E-9022-4E55-B875-7BC44EA85572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -16780,6 +16780,15 @@
       <c r="G508" t="s">
         <v>24</v>
       </c>
+      <c r="H508">
+        <v>87</v>
+      </c>
+      <c r="I508">
+        <v>98</v>
+      </c>
+      <c r="J508">
+        <v>0</v>
+      </c>
     </row>
     <row r="509" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
@@ -16803,6 +16812,15 @@
       <c r="G509" t="s">
         <v>25</v>
       </c>
+      <c r="H509">
+        <v>98</v>
+      </c>
+      <c r="I509">
+        <v>87</v>
+      </c>
+      <c r="J509">
+        <v>0</v>
+      </c>
     </row>
     <row r="510" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
@@ -16826,6 +16844,15 @@
       <c r="G510" t="s">
         <v>24</v>
       </c>
+      <c r="H510">
+        <v>84</v>
+      </c>
+      <c r="I510">
+        <v>82</v>
+      </c>
+      <c r="J510">
+        <v>0</v>
+      </c>
     </row>
     <row r="511" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
@@ -16848,6 +16875,15 @@
       </c>
       <c r="G511" t="s">
         <v>25</v>
+      </c>
+      <c r="H511">
+        <v>82</v>
+      </c>
+      <c r="I511">
+        <v>84</v>
+      </c>
+      <c r="J511">
+        <v>0</v>
       </c>
     </row>
     <row r="512" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F851A15E-9022-4E55-B875-7BC44EA85572}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CA62C4-2CBF-45FD-A80C-5E1199FC16E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -16908,8 +16908,17 @@
       <c r="G512" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H512">
+        <v>82</v>
+      </c>
+      <c r="I512">
+        <v>75</v>
+      </c>
+      <c r="J512">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>46249</v>
       </c>
@@ -16931,8 +16940,17 @@
       <c r="G513" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H513">
+        <v>75</v>
+      </c>
+      <c r="I513">
+        <v>82</v>
+      </c>
+      <c r="J513">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>46249</v>
       </c>
@@ -16954,8 +16972,17 @@
       <c r="G514" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H514">
+        <v>70</v>
+      </c>
+      <c r="I514">
+        <v>80</v>
+      </c>
+      <c r="J514">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>46249</v>
       </c>
@@ -16977,8 +17004,17 @@
       <c r="G515" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H515">
+        <v>80</v>
+      </c>
+      <c r="I515">
+        <v>70</v>
+      </c>
+      <c r="J515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>46249</v>
       </c>
@@ -17000,8 +17036,17 @@
       <c r="G516" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H516">
+        <v>92</v>
+      </c>
+      <c r="I516">
+        <v>87</v>
+      </c>
+      <c r="J516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>46249</v>
       </c>
@@ -17023,8 +17068,17 @@
       <c r="G517" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H517">
+        <v>87</v>
+      </c>
+      <c r="I517">
+        <v>92</v>
+      </c>
+      <c r="J517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>46250</v>
       </c>
@@ -17047,7 +17101,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>46250</v>
       </c>
@@ -17070,7 +17124,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>46250</v>
       </c>
@@ -17093,7 +17147,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>46250</v>
       </c>
@@ -17116,7 +17170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>46250</v>
       </c>
@@ -17139,7 +17193,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>46250</v>
       </c>
@@ -17162,7 +17216,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>46251</v>
       </c>
@@ -17185,7 +17239,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>46251</v>
       </c>
@@ -17208,7 +17262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>46252</v>
       </c>
@@ -17231,7 +17285,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>46252</v>
       </c>
@@ -17254,7 +17308,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>46252</v>
       </c>

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CA62C4-2CBF-45FD-A80C-5E1199FC16E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F99E04-6963-4F46-A01F-DBFB365499D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -17100,6 +17100,15 @@
       <c r="G518" t="s">
         <v>24</v>
       </c>
+      <c r="H518">
+        <v>95</v>
+      </c>
+      <c r="I518">
+        <v>91</v>
+      </c>
+      <c r="J518">
+        <v>1</v>
+      </c>
     </row>
     <row r="519" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
@@ -17123,6 +17132,15 @@
       <c r="G519" t="s">
         <v>25</v>
       </c>
+      <c r="H519">
+        <v>91</v>
+      </c>
+      <c r="I519">
+        <v>95</v>
+      </c>
+      <c r="J519">
+        <v>1</v>
+      </c>
     </row>
     <row r="520" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
@@ -17146,6 +17164,15 @@
       <c r="G520" t="s">
         <v>24</v>
       </c>
+      <c r="H520">
+        <v>88</v>
+      </c>
+      <c r="I520">
+        <v>85</v>
+      </c>
+      <c r="J520">
+        <v>0</v>
+      </c>
     </row>
     <row r="521" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
@@ -17169,6 +17196,15 @@
       <c r="G521" t="s">
         <v>25</v>
       </c>
+      <c r="H521">
+        <v>85</v>
+      </c>
+      <c r="I521">
+        <v>88</v>
+      </c>
+      <c r="J521">
+        <v>0</v>
+      </c>
     </row>
     <row r="522" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
@@ -17192,6 +17228,15 @@
       <c r="G522" t="s">
         <v>24</v>
       </c>
+      <c r="H522">
+        <v>82</v>
+      </c>
+      <c r="I522">
+        <v>80</v>
+      </c>
+      <c r="J522">
+        <v>0</v>
+      </c>
     </row>
     <row r="523" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
@@ -17214,6 +17259,15 @@
       </c>
       <c r="G523" t="s">
         <v>25</v>
+      </c>
+      <c r="H523">
+        <v>80</v>
+      </c>
+      <c r="I523">
+        <v>82</v>
+      </c>
+      <c r="J523">
+        <v>0</v>
       </c>
     </row>
     <row r="524" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F99E04-6963-4F46-A01F-DBFB365499D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A765070-67B8-4452-959E-43F16E8F805E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -17292,6 +17292,15 @@
       <c r="G524" t="s">
         <v>24</v>
       </c>
+      <c r="H524">
+        <v>70</v>
+      </c>
+      <c r="I524">
+        <v>78</v>
+      </c>
+      <c r="J524">
+        <v>0</v>
+      </c>
     </row>
     <row r="525" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
@@ -17314,6 +17323,15 @@
       </c>
       <c r="G525" t="s">
         <v>25</v>
+      </c>
+      <c r="H525">
+        <v>78</v>
+      </c>
+      <c r="I525">
+        <v>70</v>
+      </c>
+      <c r="J525">
+        <v>0</v>
       </c>
     </row>
     <row r="526" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A765070-67B8-4452-959E-43F16E8F805E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED22D03-304D-4817-B40C-C9AE8B9A0D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -17356,6 +17356,15 @@
       <c r="G526" t="s">
         <v>24</v>
       </c>
+      <c r="H526">
+        <v>86</v>
+      </c>
+      <c r="I526">
+        <v>93</v>
+      </c>
+      <c r="J526">
+        <v>0</v>
+      </c>
     </row>
     <row r="527" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
@@ -17379,6 +17388,15 @@
       <c r="G527" t="s">
         <v>25</v>
       </c>
+      <c r="H527">
+        <v>93</v>
+      </c>
+      <c r="I527">
+        <v>86</v>
+      </c>
+      <c r="J527">
+        <v>0</v>
+      </c>
     </row>
     <row r="528" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
@@ -17402,8 +17420,17 @@
       <c r="G528" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H528">
+        <v>77</v>
+      </c>
+      <c r="I528">
+        <v>85</v>
+      </c>
+      <c r="J528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="529" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>46252</v>
       </c>
@@ -17425,8 +17452,17 @@
       <c r="G529" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H529">
+        <v>85</v>
+      </c>
+      <c r="I529">
+        <v>77</v>
+      </c>
+      <c r="J529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="530" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>46252</v>
       </c>
@@ -17448,8 +17484,17 @@
       <c r="G530" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H530">
+        <v>97</v>
+      </c>
+      <c r="I530">
+        <v>82</v>
+      </c>
+      <c r="J530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="531" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>46252</v>
       </c>
@@ -17471,8 +17516,17 @@
       <c r="G531" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="532" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H531">
+        <v>82</v>
+      </c>
+      <c r="I531">
+        <v>97</v>
+      </c>
+      <c r="J531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>46252</v>
       </c>
@@ -17494,8 +17548,17 @@
       <c r="G532" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="533" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H532">
+        <v>101</v>
+      </c>
+      <c r="I532">
+        <v>95</v>
+      </c>
+      <c r="J532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>46252</v>
       </c>
@@ -17517,8 +17580,17 @@
       <c r="G533" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="534" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H533">
+        <v>95</v>
+      </c>
+      <c r="I533">
+        <v>101</v>
+      </c>
+      <c r="J533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>46253</v>
       </c>
@@ -17541,7 +17613,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="535" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>46253</v>
       </c>
@@ -17564,7 +17636,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="536" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>46253</v>
       </c>
@@ -17587,7 +17659,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="537" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>46253</v>
       </c>
@@ -17610,7 +17682,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="538" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>46254</v>
       </c>
@@ -17633,7 +17705,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="539" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>46254</v>
       </c>
@@ -17656,7 +17728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="540" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>46254</v>
       </c>
@@ -17679,7 +17751,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="541" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>46254</v>
       </c>
@@ -17702,7 +17774,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="542" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>46254</v>
       </c>
@@ -17725,7 +17797,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="543" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>46254</v>
       </c>
@@ -17748,7 +17820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="544" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>46255</v>
       </c>

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED22D03-304D-4817-B40C-C9AE8B9A0D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E81A85E-91EC-47F3-9C7F-7F7782C88B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -17612,6 +17612,15 @@
       <c r="G534" t="s">
         <v>24</v>
       </c>
+      <c r="H534">
+        <v>77</v>
+      </c>
+      <c r="I534">
+        <v>66</v>
+      </c>
+      <c r="J534">
+        <v>0</v>
+      </c>
     </row>
     <row r="535" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
@@ -17635,6 +17644,15 @@
       <c r="G535" t="s">
         <v>25</v>
       </c>
+      <c r="H535">
+        <v>66</v>
+      </c>
+      <c r="I535">
+        <v>77</v>
+      </c>
+      <c r="J535">
+        <v>0</v>
+      </c>
     </row>
     <row r="536" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
@@ -17658,6 +17676,15 @@
       <c r="G536" t="s">
         <v>24</v>
       </c>
+      <c r="H536">
+        <v>82</v>
+      </c>
+      <c r="I536">
+        <v>93</v>
+      </c>
+      <c r="J536">
+        <v>0</v>
+      </c>
     </row>
     <row r="537" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
@@ -17680,6 +17707,15 @@
       </c>
       <c r="G537" t="s">
         <v>25</v>
+      </c>
+      <c r="H537">
+        <v>93</v>
+      </c>
+      <c r="I537">
+        <v>82</v>
+      </c>
+      <c r="J537">
+        <v>0</v>
       </c>
     </row>
     <row r="538" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E81A85E-91EC-47F3-9C7F-7F7782C88B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A23A9C1-CF9D-41E2-94DA-F518A8E9CCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -17740,6 +17740,15 @@
       <c r="G538" t="s">
         <v>24</v>
       </c>
+      <c r="H538">
+        <v>85</v>
+      </c>
+      <c r="I538">
+        <v>91</v>
+      </c>
+      <c r="J538">
+        <v>0</v>
+      </c>
     </row>
     <row r="539" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
@@ -17763,6 +17772,15 @@
       <c r="G539" t="s">
         <v>25</v>
       </c>
+      <c r="H539">
+        <v>91</v>
+      </c>
+      <c r="I539">
+        <v>85</v>
+      </c>
+      <c r="J539">
+        <v>0</v>
+      </c>
     </row>
     <row r="540" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
@@ -17786,6 +17804,15 @@
       <c r="G540" t="s">
         <v>24</v>
       </c>
+      <c r="H540">
+        <v>124</v>
+      </c>
+      <c r="I540">
+        <v>88</v>
+      </c>
+      <c r="J540">
+        <v>0</v>
+      </c>
     </row>
     <row r="541" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
@@ -17809,6 +17836,15 @@
       <c r="G541" t="s">
         <v>25</v>
       </c>
+      <c r="H541">
+        <v>88</v>
+      </c>
+      <c r="I541">
+        <v>124</v>
+      </c>
+      <c r="J541">
+        <v>0</v>
+      </c>
     </row>
     <row r="542" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
@@ -17832,6 +17868,15 @@
       <c r="G542" t="s">
         <v>24</v>
       </c>
+      <c r="H542">
+        <v>78</v>
+      </c>
+      <c r="I542">
+        <v>101</v>
+      </c>
+      <c r="J542">
+        <v>0</v>
+      </c>
     </row>
     <row r="543" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
@@ -17854,6 +17899,15 @@
       </c>
       <c r="G543" t="s">
         <v>25</v>
+      </c>
+      <c r="H543">
+        <v>101</v>
+      </c>
+      <c r="I543">
+        <v>78</v>
+      </c>
+      <c r="J543">
+        <v>0</v>
       </c>
     </row>
     <row r="544" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A23A9C1-CF9D-41E2-94DA-F518A8E9CCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB253C7-9997-415D-B4DF-04EF47054336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -17932,8 +17932,17 @@
       <c r="G544" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H544">
+        <v>70</v>
+      </c>
+      <c r="I544">
+        <v>73</v>
+      </c>
+      <c r="J544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>46255</v>
       </c>
@@ -17955,8 +17964,17 @@
       <c r="G545" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H545">
+        <v>73</v>
+      </c>
+      <c r="I545">
+        <v>70</v>
+      </c>
+      <c r="J545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>46255</v>
       </c>
@@ -17978,8 +17996,17 @@
       <c r="G546" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H546">
+        <v>79</v>
+      </c>
+      <c r="I546">
+        <v>82</v>
+      </c>
+      <c r="J546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="547" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>46255</v>
       </c>
@@ -18001,8 +18028,17 @@
       <c r="G547" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H547">
+        <v>82</v>
+      </c>
+      <c r="I547">
+        <v>79</v>
+      </c>
+      <c r="J547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>46255</v>
       </c>
@@ -18024,8 +18060,17 @@
       <c r="G548" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H548">
+        <v>94</v>
+      </c>
+      <c r="I548">
+        <v>84</v>
+      </c>
+      <c r="J548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>46255</v>
       </c>
@@ -18047,8 +18092,17 @@
       <c r="G549" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H549">
+        <v>84</v>
+      </c>
+      <c r="I549">
+        <v>94</v>
+      </c>
+      <c r="J549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>46256</v>
       </c>
@@ -18071,7 +18125,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>46256</v>
       </c>
@@ -18094,7 +18148,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>46256</v>
       </c>
@@ -18117,7 +18171,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>46256</v>
       </c>
@@ -18140,7 +18194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>46256</v>
       </c>
@@ -18163,7 +18217,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>46256</v>
       </c>
@@ -18186,7 +18240,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>46257</v>
       </c>
@@ -18209,7 +18263,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>46257</v>
       </c>
@@ -18232,7 +18286,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>46257</v>
       </c>
@@ -18255,7 +18309,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>46257</v>
       </c>
@@ -18278,7 +18332,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>46257</v>
       </c>

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB253C7-9997-415D-B4DF-04EF47054336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC163805-3337-492D-9619-A2ACF60A1064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -18124,6 +18124,15 @@
       <c r="G550" t="s">
         <v>24</v>
       </c>
+      <c r="H550">
+        <v>68</v>
+      </c>
+      <c r="I550">
+        <v>77</v>
+      </c>
+      <c r="J550">
+        <v>0</v>
+      </c>
     </row>
     <row r="551" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
@@ -18147,6 +18156,15 @@
       <c r="G551" t="s">
         <v>25</v>
       </c>
+      <c r="H551">
+        <v>77</v>
+      </c>
+      <c r="I551">
+        <v>68</v>
+      </c>
+      <c r="J551">
+        <v>0</v>
+      </c>
     </row>
     <row r="552" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
@@ -18170,6 +18188,15 @@
       <c r="G552" t="s">
         <v>24</v>
       </c>
+      <c r="H552">
+        <v>102</v>
+      </c>
+      <c r="I552">
+        <v>109</v>
+      </c>
+      <c r="J552">
+        <v>0</v>
+      </c>
     </row>
     <row r="553" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
@@ -18193,6 +18220,15 @@
       <c r="G553" t="s">
         <v>25</v>
       </c>
+      <c r="H553">
+        <v>109</v>
+      </c>
+      <c r="I553">
+        <v>102</v>
+      </c>
+      <c r="J553">
+        <v>0</v>
+      </c>
     </row>
     <row r="554" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
@@ -18216,6 +18252,15 @@
       <c r="G554" t="s">
         <v>24</v>
       </c>
+      <c r="H554">
+        <v>99</v>
+      </c>
+      <c r="I554">
+        <v>89</v>
+      </c>
+      <c r="J554">
+        <v>0</v>
+      </c>
     </row>
     <row r="555" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
@@ -18238,6 +18283,15 @@
       </c>
       <c r="G555" t="s">
         <v>25</v>
+      </c>
+      <c r="H555">
+        <v>89</v>
+      </c>
+      <c r="I555">
+        <v>99</v>
+      </c>
+      <c r="J555">
+        <v>0</v>
       </c>
     </row>
     <row r="556" spans="1:10" x14ac:dyDescent="0.35">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC163805-3337-492D-9619-A2ACF60A1064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99A1AC3-7A60-4FBA-B051-95BC6DF96473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -16973,10 +16973,10 @@
         <v>24</v>
       </c>
       <c r="H514">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="I514">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="J514">
         <v>0</v>
@@ -17005,10 +17005,10 @@
         <v>25</v>
       </c>
       <c r="H515">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I515">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="J515">
         <v>0</v>
@@ -17037,10 +17037,10 @@
         <v>24</v>
       </c>
       <c r="H516">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="I516">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J516">
         <v>0</v>
@@ -17069,10 +17069,10 @@
         <v>25</v>
       </c>
       <c r="H517">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="I517">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="J517">
         <v>0</v>

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TRACERsports\DBs\wnba\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D99A1AC3-7A60-4FBA-B051-95BC6DF96473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06498F10-2194-4593-AEDD-EFE8C8AF5695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{1654EDFA-4626-4D72-A032-E72CC9A130FE}"/>
   </bookViews>
@@ -18316,6 +18316,15 @@
       <c r="G556" t="s">
         <v>24</v>
       </c>
+      <c r="H556">
+        <v>113</v>
+      </c>
+      <c r="I556">
+        <v>90</v>
+      </c>
+      <c r="J556">
+        <v>0</v>
+      </c>
     </row>
     <row r="557" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
@@ -18339,6 +18348,15 @@
       <c r="G557" t="s">
         <v>25</v>
       </c>
+      <c r="H557">
+        <v>90</v>
+      </c>
+      <c r="I557">
+        <v>113</v>
+      </c>
+      <c r="J557">
+        <v>0</v>
+      </c>
     </row>
     <row r="558" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
@@ -18362,6 +18380,15 @@
       <c r="G558" t="s">
         <v>24</v>
       </c>
+      <c r="H558">
+        <v>70</v>
+      </c>
+      <c r="I558">
+        <v>92</v>
+      </c>
+      <c r="J558">
+        <v>0</v>
+      </c>
     </row>
     <row r="559" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
@@ -18385,6 +18412,15 @@
       <c r="G559" t="s">
         <v>25</v>
       </c>
+      <c r="H559">
+        <v>92</v>
+      </c>
+      <c r="I559">
+        <v>70</v>
+      </c>
+      <c r="J559">
+        <v>0</v>
+      </c>
     </row>
     <row r="560" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
@@ -18408,8 +18444,17 @@
       <c r="G560" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H560">
+        <v>105</v>
+      </c>
+      <c r="I560">
+        <v>100</v>
+      </c>
+      <c r="J560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="561" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>46257</v>
       </c>
@@ -18431,8 +18476,17 @@
       <c r="G561" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H561">
+        <v>100</v>
+      </c>
+      <c r="I561">
+        <v>105</v>
+      </c>
+      <c r="J561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="562" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>46257</v>
       </c>
@@ -18454,8 +18508,17 @@
       <c r="G562" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H562">
+        <v>88</v>
+      </c>
+      <c r="I562">
+        <v>78</v>
+      </c>
+      <c r="J562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="563" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>46257</v>
       </c>
@@ -18477,8 +18540,17 @@
       <c r="G563" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H563">
+        <v>78</v>
+      </c>
+      <c r="I563">
+        <v>88</v>
+      </c>
+      <c r="J563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="564" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>46258</v>
       </c>
@@ -18501,7 +18573,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>46258</v>
       </c>
@@ -18524,7 +18596,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>46258</v>
       </c>
@@ -18547,7 +18619,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>46258</v>
       </c>
@@ -18570,7 +18642,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>46259</v>
       </c>
@@ -18593,7 +18665,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>46259</v>
       </c>
@@ -18616,7 +18688,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>46259</v>
       </c>
@@ -18639,7 +18711,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>46259</v>
       </c>
@@ -18662,7 +18734,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>46259</v>
       </c>
@@ -18685,7 +18757,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>46259</v>
       </c>
@@ -18708,7 +18780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>46260</v>
       </c>
@@ -18731,7 +18803,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>46260</v>
       </c>
@@ -18754,7 +18826,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>46260</v>
       </c>

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -25342,6 +25342,15 @@
           <t>A</t>
         </is>
       </c>
+      <c r="H592" t="n">
+        <v>66</v>
+      </c>
+      <c r="I592" t="n">
+        <v>85</v>
+      </c>
+      <c r="J592" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="1" t="n">
@@ -25375,6 +25384,15 @@
           <t>H</t>
         </is>
       </c>
+      <c r="H593" t="n">
+        <v>85</v>
+      </c>
+      <c r="I593" t="n">
+        <v>66</v>
+      </c>
+      <c r="J593" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="1" t="n">
@@ -25408,6 +25426,15 @@
           <t>A</t>
         </is>
       </c>
+      <c r="H594" t="n">
+        <v>69</v>
+      </c>
+      <c r="I594" t="n">
+        <v>101</v>
+      </c>
+      <c r="J594" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="1" t="n">
@@ -25440,6 +25467,15 @@
         <is>
           <t>H</t>
         </is>
+      </c>
+      <c r="H595" t="n">
+        <v>101</v>
+      </c>
+      <c r="I595" t="n">
+        <v>69</v>
+      </c>
+      <c r="J595" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="596">

--- a/DBs/wnba/Results/WNBA_2026_Results.xlsx
+++ b/DBs/wnba/Results/WNBA_2026_Results.xlsx
@@ -25510,6 +25510,15 @@
           <t>A</t>
         </is>
       </c>
+      <c r="H596" t="n">
+        <v>81</v>
+      </c>
+      <c r="I596" t="n">
+        <v>89</v>
+      </c>
+      <c r="J596" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="1" t="n">
@@ -25543,6 +25552,15 @@
           <t>H</t>
         </is>
       </c>
+      <c r="H597" t="n">
+        <v>89</v>
+      </c>
+      <c r="I597" t="n">
+        <v>81</v>
+      </c>
+      <c r="J597" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="1" t="n">
@@ -25576,6 +25594,15 @@
           <t>A</t>
         </is>
       </c>
+      <c r="H598" t="n">
+        <v>71</v>
+      </c>
+      <c r="I598" t="n">
+        <v>97</v>
+      </c>
+      <c r="J598" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="1" t="n">
@@ -25609,6 +25636,15 @@
           <t>H</t>
         </is>
       </c>
+      <c r="H599" t="n">
+        <v>97</v>
+      </c>
+      <c r="I599" t="n">
+        <v>71</v>
+      </c>
+      <c r="J599" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="1" t="n">
@@ -25642,6 +25678,15 @@
           <t>A</t>
         </is>
       </c>
+      <c r="H600" t="n">
+        <v>86</v>
+      </c>
+      <c r="I600" t="n">
+        <v>69</v>
+      </c>
+      <c r="J600" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="1" t="n">
@@ -25675,6 +25720,15 @@
           <t>H</t>
         </is>
       </c>
+      <c r="H601" t="n">
+        <v>69</v>
+      </c>
+      <c r="I601" t="n">
+        <v>86</v>
+      </c>
+      <c r="J601" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="1" t="n">
@@ -25708,6 +25762,15 @@
           <t>A</t>
         </is>
       </c>
+      <c r="H602" t="n">
+        <v>90</v>
+      </c>
+      <c r="I602" t="n">
+        <v>74</v>
+      </c>
+      <c r="J602" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="1" t="n">
@@ -25740,6 +25803,15 @@
         <is>
           <t>H</t>
         </is>
+      </c>
+      <c r="H603" t="n">
+        <v>74</v>
+      </c>
+      <c r="I603" t="n">
+        <v>90</v>
+      </c>
+      <c r="J603" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="604">
